--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32986800</v>
+        <v>36514.69</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>47980500</v>
+        <v>53111.95</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>58799580</v>
+        <v>65088.11</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>25199820</v>
+        <v>27894.91</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>22980000</v>
+        <v>25437.68</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7875000</v>
+        <v>8717.219999999999</v>
       </c>
     </row>
     <row r="8">
@@ -931,17 +931,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>58499700</v>
+        <v>64756.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3710-375-CM26</t>
+          <t>2771-366-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,48 +961,48 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6900000</v>
+        <v>10624.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2771-366-CM26</t>
+          <t>1485217-83-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,48 +1022,48 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9598000</v>
+        <v>1582.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1485217-83-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,48 +1083,48 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1430000</v>
+        <v>103347.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>3710-375-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,48 +1144,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>93362782</v>
+        <v>7637.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>934-81-CM26</t>
+          <t>1057387-333-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,53 +1200,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1389000</v>
+        <v>66151.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057387-333-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,43 +1271,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>59760000</v>
+        <v>11980.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,48 +1327,48 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10823050</v>
+        <v>22138.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1408,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>19999400</v>
+        <v>27147.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>2467-743-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,43 +1454,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24525000</v>
+        <v>1374.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2467-743-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,43 +1515,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1242000</v>
+        <v>6929.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>2360-405-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,43 +1576,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6260000</v>
+        <v>17934.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2360-405-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,43 +1637,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16202088</v>
+        <v>1379.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>4404-131-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1246336</v>
+        <v>8608.190000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4404-131-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,43 +1759,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t xml:space="preserve">FELIPE </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7776500</v>
+        <v>22018.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>2467-740-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,43 +1820,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1730001</v>
+        <v>911.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2467-740-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,43 +1881,43 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>823200</v>
+        <v>1915.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1413021-18-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,43 +1942,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.804.011-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>19890800</v>
+        <v>33208.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,43 +2003,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>29999995</v>
+        <v>22138.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>5522-57-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,43 +2064,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>20000000</v>
+        <v>1162.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5522-57-CM26</t>
+          <t>1391-1204-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,48 +2120,48 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t xml:space="preserve">RENTUR CHILE SPA </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.241.697-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1050000</v>
+        <v>11069.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1391-1204-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,53 +2176,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.241.697-2</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>10000000</v>
+        <v>2213.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2273,17 +2273,17 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2000000</v>
+        <v>1372.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,48 +2303,48 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1240000</v>
+        <v>1660.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,43 +2369,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1500000</v>
+        <v>77265.00999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>5178-2776-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,28 +2445,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>69800000</v>
+        <v>1649.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5178-2776-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,53 +2481,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1490000</v>
+        <v>31880.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,43 +2552,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>28800000</v>
+        <v>11955.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,43 +2613,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10800000</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2700,17 +2700,17 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>70000</v>
+        <v>1660.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,98 +2735,37 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1062807-63-CM26</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>62.000.590-8</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>DAVID ISAAC</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>200000000</v>
+        <v>221389.72</v>
       </c>
     </row>
   </sheetData>
